--- a/descriptives_by_sensor_table.xlsx
+++ b/descriptives_by_sensor_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
   <si>
     <t xml:space="preserve">Characteristic
 </t>
@@ -117,6 +117,24 @@
     <t xml:space="preserve">    Sí</t>
   </si>
   <si>
+    <t xml:space="preserve">ses_level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    NSE E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    NSE D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    NSE C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    NSE B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    NSE A</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mean (SD); n (%)</t>
   </si>
   <si>
@@ -138,6 +156,9 @@
   </si>
   <si>
     <t xml:space="preserve">1,061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,057</t>
   </si>
   <si>
     <t xml:space="preserve">GEOHealth_Carab_VictorRaulHT
@@ -246,6 +267,18 @@
     <t xml:space="preserve">39 (72%)</t>
   </si>
   <si>
+    <t xml:space="preserve">4 (7.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (1.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 (58%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (5.7%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">GEOHealth_MiPeru_Chavinillo
 N = 501
 </t>
@@ -326,6 +359,21 @@
     <t xml:space="preserve">186 (37%)</t>
   </si>
   <si>
+    <t xml:space="preserve">32 (6.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53 (11%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161 (32%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218 (44%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36 (7.2%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">GEOHealth_PuenteP_Estadio_1
 N = 361
 </t>
@@ -406,6 +454,21 @@
     <t xml:space="preserve">142 (39%)</t>
   </si>
   <si>
+    <t xml:space="preserve">14 (3.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 (8.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112 (31%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169 (47%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 (8.7%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">GEOHealth_SanMa_IE005
 N = 127
 </t>
@@ -483,6 +546,18 @@
     <t xml:space="preserve">47 (37%)</t>
   </si>
   <si>
+    <t xml:space="preserve">7 (5.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (7.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43 (34%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59 (47%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">GEOHealth_Ventanilla_NSBelen
 N = 19
 </t>
@@ -534,6 +609,12 @@
   </si>
   <si>
     <t xml:space="preserve">10 (53%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (42%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (5.3%)</t>
   </si>
   <si>
     <t xml:space="preserve">p-value
@@ -993,28 +1074,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" ht="NA" customHeight="1">
@@ -1022,25 +1103,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="I2" s="8" t="n">
         <v>0.5</v>
@@ -1051,25 +1132,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I3" s="9" t="n">
         <v>0.4</v>
@@ -1080,28 +1161,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" ht="NA" customHeight="1">
@@ -1109,28 +1190,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" ht="NA" customHeight="1">
@@ -1141,22 +1222,22 @@
         <v>753</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="I6" s="9" t="n">
         <v>0.6</v>
@@ -1167,7 +1248,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>1</v>
@@ -1188,7 +1269,7 @@
         <v>5</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" ht="NA" customHeight="1">
@@ -1199,22 +1280,22 @@
         <v>328</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="I8" s="9" t="n">
         <v>0.5</v>
@@ -1225,7 +1306,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>4</v>
@@ -1246,7 +1327,7 @@
         <v>17</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" ht="NA" customHeight="1">
@@ -1254,25 +1335,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I10" s="9" t="n">
         <v>0.2</v>
@@ -1283,28 +1364,28 @@
         <v>9</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" ht="NA" customHeight="1">
@@ -1312,28 +1393,28 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" ht="NA" customHeight="1">
@@ -1341,28 +1422,28 @@
         <v>11</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" ht="NA" customHeight="1">
@@ -1370,28 +1451,28 @@
         <v>12</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15" ht="NA" customHeight="1">
@@ -1399,28 +1480,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" ht="NA" customHeight="1">
@@ -1428,28 +1509,28 @@
         <v>14</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" ht="NA" customHeight="1">
@@ -1457,28 +1538,28 @@
         <v>15</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" ht="NA" customHeight="1">
@@ -1486,7 +1567,7 @@
         <v>6</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>0</v>
@@ -1507,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" ht="NA" customHeight="1">
@@ -1515,25 +1596,25 @@
         <v>16</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="I19" s="9" t="n">
         <v>0.2</v>
@@ -1544,7 +1625,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>0</v>
@@ -1565,7 +1646,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" ht="NA" customHeight="1">
@@ -1573,28 +1654,28 @@
         <v>17</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="22" ht="NA" customHeight="1">
@@ -1602,28 +1683,28 @@
         <v>9</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" ht="NA" customHeight="1">
@@ -1631,28 +1712,28 @@
         <v>18</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" ht="NA" customHeight="1">
@@ -1660,7 +1741,7 @@
         <v>6</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>0</v>
@@ -1681,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" ht="NA" customHeight="1">
@@ -1689,28 +1770,28 @@
         <v>19</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="26" ht="NA" customHeight="1">
@@ -1718,28 +1799,28 @@
         <v>20</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" ht="NA" customHeight="1">
@@ -1747,28 +1828,28 @@
         <v>21</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" ht="NA" customHeight="1">
@@ -1776,25 +1857,25 @@
         <v>22</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I28" s="9" t="n">
         <v>0.2</v>
@@ -1805,28 +1886,28 @@
         <v>23</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" ht="NA" customHeight="1">
@@ -1834,28 +1915,28 @@
         <v>24</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" ht="NA" customHeight="1">
@@ -1863,28 +1944,28 @@
         <v>25</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" ht="NA" customHeight="1">
@@ -1892,28 +1973,28 @@
         <v>26</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" ht="NA" customHeight="1">
@@ -1921,28 +2002,28 @@
         <v>27</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="34" ht="NA" customHeight="1">
@@ -1950,28 +2031,28 @@
         <v>28</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" ht="NA" customHeight="1">
@@ -1979,28 +2060,28 @@
         <v>29</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" ht="NA" customHeight="1">
@@ -2008,28 +2089,28 @@
         <v>30</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37" ht="NA" customHeight="1">
@@ -2037,7 +2118,7 @@
         <v>6</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C37" s="9" t="n">
         <v>0</v>
@@ -2058,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" ht="NA" customHeight="1">
@@ -2066,25 +2147,25 @@
         <v>31</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I38" s="9" t="n">
         <v>0.7</v>
@@ -2095,121 +2176,324 @@
         <v>32</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40" ht="NA" customHeight="1">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="F40" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="H40" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="I40" s="10" t="s">
-        <v>38</v>
+      <c r="B40" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="41" ht="NA" customHeight="1">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>34</v>
+      <c r="B41" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="I41" s="9" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="42" ht="NA" customHeight="1">
       <c r="A42" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>35</v>
+      <c r="B42" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" ht="NA" customHeight="1">
+      <c r="A43" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" ht="NA" customHeight="1">
+      <c r="A44" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" ht="NA" customHeight="1">
+      <c r="A45" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" ht="NA" customHeight="1">
+      <c r="A46" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" ht="NA" customHeight="1">
+      <c r="A47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C47" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G47" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" ht="NA" customHeight="1">
+      <c r="A48" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" ht="NA" customHeight="1">
+      <c r="A49" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A49:I49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/descriptives_by_sensor_table.xlsx
+++ b/descriptives_by_sensor_table.xlsx
@@ -1472,7 +1472,7 @@
         <v>44</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15" ht="NA" customHeight="1">
@@ -1675,7 +1675,7 @@
         <v>44</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="22" ht="NA" customHeight="1">

--- a/descriptives_by_sensor_table.xlsx
+++ b/descriptives_by_sensor_table.xlsx
@@ -2023,7 +2023,7 @@
         <v>44</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="34" ht="NA" customHeight="1">

--- a/descriptives_by_sensor_table.xlsx
+++ b/descriptives_by_sensor_table.xlsx
@@ -1791,7 +1791,7 @@
         <v>44</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="26" ht="NA" customHeight="1">
@@ -2023,7 +2023,7 @@
         <v>44</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="34" ht="NA" customHeight="1">
